--- a/webapp/backend/samples/Core_Elec_Platform_Landscape.xlsx
+++ b/webapp/backend/samples/Core_Elec_Platform_Landscape.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How_To" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shape_Library" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Line_Rules" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diagrams" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nodes" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Edges" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="How_To" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Shape_Library" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Line_Rules" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Diagrams" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Nodes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Edges" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -456,7 +456,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="58" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -516,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -831,6 +830,153 @@
       <c r="K6" t="inlineStr">
         <is>
           <t>Same as consumer, two-line label</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>data_store</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>cylinder</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>140</v>
+      </c>
+      <c r="E7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F7" t="n">
+        <v>140</v>
+      </c>
+      <c r="G7" t="n">
+        <v>40</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>#FFE6CC</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>#D79B00</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Downstream data store (Capital Design Database)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>report</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>wavy bottom</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>140</v>
+      </c>
+      <c r="E8" t="n">
+        <v>50</v>
+      </c>
+      <c r="F8" t="n">
+        <v>140</v>
+      </c>
+      <c r="G8" t="n">
+        <v>40</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>#FFE6CC</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>#D79B00</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Generated artifact/report output</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>tier_summary</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>rounded rectangle</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>170</v>
+      </c>
+      <c r="E9" t="n">
+        <v>60</v>
+      </c>
+      <c r="F9" t="n">
+        <v>150</v>
+      </c>
+      <c r="G9" t="n">
+        <v>50</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>#F0F0F0</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>#888888</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Summary box for the context-level (D2) diagram</t>
         </is>
       </c>
     </row>
@@ -973,7 +1119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1043,6 +1189,33 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>EA-CEP-CTX</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Core Elec Platform — Context View</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>left-right</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Simplified 3-tier context view</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1054,7 +1227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1138,6 +1311,11 @@
           <t>CONV_SRC</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Z_SOURCE</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>source_system</t>
@@ -1166,6 +1344,11 @@
           <t>EXT_SYS</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Z_SOURCE</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>source_system</t>
@@ -1229,7 +1412,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Capital</t>
+          <t>Capital (Design App)</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1250,6 +1433,11 @@
           <t>LEGACY</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Z_CONSUMERS</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>consumer_multi</t>
@@ -1261,7 +1449,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -1278,9 +1466,14 @@
           <t>CONV_REP</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Z_CONSUMERS</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>report</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1289,7 +1482,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
         <v>2</v>
@@ -1306,9 +1499,14 @@
           <t>ARTIFACTS</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Z_CONSUMERS</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>report</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1317,7 +1515,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>3</v>
@@ -1334,9 +1532,14 @@
           <t>CAP_DB</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Z_CONSUMERS</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>data_store</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1345,7 +1548,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
@@ -1365,6 +1568,11 @@
           <t>APS</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Z_CONSUMERS</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>consumer</t>
@@ -1376,7 +1584,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
         <v>5</v>
@@ -1393,6 +1601,11 @@
           <t>MDMR</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Z_CONSUMERS</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>consumer</t>
@@ -1404,7 +1617,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
         <v>6</v>
@@ -1421,6 +1634,11 @@
           <t>AIRINA</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Z_CONSUMERS</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>consumer</t>
@@ -1432,7 +1650,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
         <v>7</v>
@@ -1449,6 +1667,11 @@
           <t>SKYWISE</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Z_CONSUMERS</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>consumer</t>
@@ -1460,10 +1683,427 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
         <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Z_SOURCE</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Source Systems</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>#F7F9FC</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Z_CONSUMERS</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Downstream Consumers</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>4</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>#F7FBF7</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Z_LEGEND</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Legend</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>LG_SRC</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Z_LEGEND</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>source_system</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Source system</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>110</v>
+      </c>
+      <c r="I17" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LG_BROKER</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Z_LEGEND</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>broker</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Central broker</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>110</v>
+      </c>
+      <c r="I18" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>LG_APP</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Z_LEGEND</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>target_app</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Peer design app</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" t="n">
+        <v>110</v>
+      </c>
+      <c r="I19" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LG_CONS</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Z_LEGEND</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>consumer</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Consumer system</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" t="n">
+        <v>110</v>
+      </c>
+      <c r="I20" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LG_DATA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Z_LEGEND</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>data_store</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data store</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" t="n">
+        <v>110</v>
+      </c>
+      <c r="I21" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>LG_REPORT</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Z_LEGEND</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>report</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Report / artifact</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" t="n">
+        <v>110</v>
+      </c>
+      <c r="I22" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CTX_SRC</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>tier_summary</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Source Systems</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CTX_CORE</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>tier_summary</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Integration Core</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CTX_CONSUMERS</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>tier_summary</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Downstream Consumers</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>3</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1477,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1650,7 +2290,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>IN: XML Input, Conv Data, Effectivity</t>
+          <t>Design &amp; conversion inputs</t>
         </is>
       </c>
     </row>
@@ -1682,7 +2322,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>OUT: 2D graphs, Design info, Artifacts, Reports, Metadata, API data</t>
+          <t>Design outputs</t>
         </is>
       </c>
     </row>
@@ -1939,6 +2579,70 @@
       <c r="F13" t="inlineStr">
         <is>
           <t>Scheduled API data</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ctx_e1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CTX_SRC</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CTX_CORE</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>data_flow</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Feeds</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ctx_e2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CTX_CORE</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CTX_CONSUMERS</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>data_flow</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Serves</t>
         </is>
       </c>
     </row>
